--- a/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/00_작성요청_정리표_20261029_v3.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/00_작성요청_정리표_20261029_v3.xlsx
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05_ISO14001_IATF_회신현황_체크리스트_20261029_v3.xlsx</t>
+          <t>05_ISO14001_IATF_회신현황_체크리스트_20261029_v4.xlsx</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>ISO 14001·IATF 회신 진행(IATF U15 추가)</t>
+          <t>ISO 14001·IATF 회신 진행(IATF U15 추가, A-13·U03 기안서 확인 메모)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>11_NQA청구서_대조_지급체크_20261029.xlsx</t>
+          <t>11_NQA청구서_대조_지급체크_20261029_v2.xlsx</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/00_작성요청_정리표_20261029_v3.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/00_작성요청_정리표_20261029_v3.xlsx
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04_메시지_발송일정표_20261029_v5.xlsx</t>
+          <t>04_메시지_발송일정표_20261029_v6.xlsx</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>실제 발송한 메시지와 상태(IATF 담당 박철호 반영)</t>
+          <t>실제 발송한 메시지와 상태(42건) + 결재·지급·심사 일정 시트</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/00_작성요청_정리표_20261029_v3.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/00_작성요청_정리표_20261029_v3.xlsx
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04_메시지_발송일정표_20261029_v6.xlsx</t>
+          <t>04_메시지_발송일정표_20261029_v7.xlsx</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/00_작성요청_정리표_20261029_v3.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/00_작성요청_정리표_20261029_v3.xlsx
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04_메시지_발송일정표_20261029_v7.xlsx</t>
+          <t>04_메시지_발송일정표_20261029_v8.xlsx</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05_ISO14001_IATF_회신현황_체크리스트_20261029_v4.xlsx</t>
+          <t>05_ISO14001_IATF_회신현황_체크리스트_20261029_v5.xlsx</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06_SQ_회신현황_체크리스트_20261029_v2.xlsx</t>
+          <t>06_SQ_회신현황_체크리스트_20261029_v3.xlsx</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
